--- a/StructureDefinition-SEEHDSObservationBase.xlsx
+++ b/StructureDefinition-SEEHDSObservationBase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationBase.xlsx
+++ b/StructureDefinition-SEEHDSObservationBase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationBase.xlsx
+++ b/StructureDefinition-SEEHDSObservationBase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationBase.xlsx
+++ b/StructureDefinition-SEEHDSObservationBase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -89,10 +89,10 @@
 Profilen fångar den generella TK-mappningen och används som förälder av
 domänspecifika profiler (t.ex. SEEHDSObservationGrowth för tillväxtkurva).
 Nyckeldesignbeslut:
-- observationBody.observationValue är XOR-union av sju värdetyper (cv/pq/ivlpq/ts/ivlts/st/int).
+- observationBody.value är XOR-union av sju värdetyper (cv/pq/ivl_pq/ts/ivl_ts/st/int).
   Varje gren mappas till respektive FHIR value[x]-variant.
 - Om valueNegation=true utelämnas value[x] och dataAbsentReason sätts.
-- observationBody.time (ts/ivlts) → effective[x]; registrationTime → issued.
+- observationBody.time (ts/ivl_ts) → effective[x]; registrationTime → issued.
 - participation är polymorf (healthcareProfessional/patient/otherPerson/locationRole/resource/organisation).
   Välj FHIR-element per deltagartyp (se mappningssida).
 - PDL-fält (Sparr) hanteras via Provenance och meta.security (se mappningssida).
@@ -911,7 +911,7 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>Observationsstatus (observationBody.observationStatus – SNOMED CT urvals-id 56431000052106 → FHIR ObservationStatus via ConceptMap, se OBS-003)</t>
+    <t>Observationsstatus (observationBody.status – SNOMED CT urvals-id 56431000052106 → FHIR ObservationStatus via ConceptMap, se OBS-003)</t>
   </si>
   <si>
     <t>The status of the result value.</t>
@@ -975,7 +975,7 @@
 </t>
   </si>
   <si>
-    <t>Observationstyp (observationBody.observationType.type.code) – SNOMED CT SE OID 1.2.752.116.2.1.1; om saknas används platshållarkod</t>
+    <t>Observationstyp (observationBody.type.code) – SNOMED CT SE OID 1.2.752.116.2.1.1; om saknas används platshållarkod</t>
   </si>
   <si>
     <t>Describes what was observed. Sometimes this is called the observation "name".</t>
@@ -1044,7 +1044,7 @@
     <t>Observation.code.text</t>
   </si>
   <si>
-    <t>observationBody.observationType.type.displayName</t>
+    <t>observationBody.type.displayName</t>
   </si>
   <si>
     <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
@@ -1072,7 +1072,7 @@
 </t>
   </si>
   <si>
-    <t>Patient (observationBody.patient.person.personId om tillgängligt; annars observationBody.patient.patientId)</t>
+    <t>Patient (observationBody.patient.person.id om tillgängligt; annars observationBody.patient.id)</t>
   </si>
   <si>
     <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
@@ -1161,7 +1161,7 @@
 PeriodTiminginstant</t>
   </si>
   <si>
-    <t>Observationstid (observationBody.time.ts → effectiveDateTime; observationBody.time.ivlts → effectivePeriod); se GENERAL-001 och OBS-001</t>
+    <t>Observationstid (observationBody.time.ts → effectiveDateTime; observationBody.time.ivl_ts → effectivePeriod); se GENERAL-001 och OBS-001</t>
   </si>
   <si>
     <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
@@ -1246,14 +1246,14 @@
 CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
   </si>
   <si>
-    <t>Observationsvärde (observationBody.observationValue – XOR-union):
+    <t>Observationsvärde (observationBody.value – XOR-union):
 cv       → valueCodeableConcept
 pq       → valueQuantity
-ivlpq    → valueRange
+ivl_pq   → valueRange
 ts       → valueDateTime (precision ≥ dag) eller valueString (precision &lt; dag, se OBS-001)
-ivlts    → valuePeriod
+ivl_ts   → valuePeriod
 st       → valueString
-intValue → valueInteger
+int → valueInteger
 Om valueNegation=true utelämnas value[x] och dataAbsentReason sätts (se OBS-002).</t>
   </si>
   <si>

--- a/StructureDefinition-SEEHDSObservationBase.xlsx
+++ b/StructureDefinition-SEEHDSObservationBase.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationBase.xlsx
+++ b/StructureDefinition-SEEHDSObservationBase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationBase.xlsx
+++ b/StructureDefinition-SEEHDSObservationBase.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationBase.xlsx
+++ b/StructureDefinition-SEEHDSObservationBase.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationBase.xlsx
+++ b/StructureDefinition-SEEHDSObservationBase.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2756" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2756" uniqueCount="559">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -492,7 +492,7 @@
   <si>
     <t>Säkerhetsmärkning:
 confidentialityIndicator=true → v3-Confidentiality#R (skyddad identitet)
-approvedForPatient=false      → ActCode#NOPATIENT (ej visas för patient, se PDL-001)</t>
+approvedForPatient=false      → ActCode#NOPAT (ej visas för patient, se PDL-001)</t>
   </si>
   <si>
     <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
@@ -1557,6 +1557,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -8755,7 +8759,7 @@
         <v>485</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>105</v>
+        <v>486</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -8764,10 +8768,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8778,10 +8782,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8807,10 +8811,10 @@
         <v>482</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8861,7 +8865,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8873,7 +8877,7 @@
         <v>485</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>105</v>
+        <v>486</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8882,10 +8886,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8896,10 +8900,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8925,16 +8929,16 @@
         <v>223</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8962,10 +8966,10 @@
         <v>173</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -8983,7 +8987,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9001,10 +9005,10 @@
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>418</v>
@@ -9018,10 +9022,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9047,16 +9051,16 @@
         <v>223</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9084,10 +9088,10 @@
         <v>159</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9105,7 +9109,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9123,10 +9127,10 @@
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>418</v>
@@ -9140,10 +9144,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9166,17 +9170,17 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9225,7 +9229,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9249,7 +9253,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9260,10 +9264,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9289,10 +9293,10 @@
         <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9343,7 +9347,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9364,10 +9368,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9378,10 +9382,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9404,16 +9408,16 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9463,7 +9467,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9484,10 +9488,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9498,10 +9502,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9524,16 +9528,16 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9583,7 +9587,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9604,10 +9608,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9618,10 +9622,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9647,16 +9651,16 @@
         <v>466</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9705,7 +9709,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9726,10 +9730,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9740,10 +9744,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9858,10 +9862,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9978,10 +9982,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10100,10 +10104,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10129,13 +10133,13 @@
         <v>223</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O67" t="s" s="2">
         <v>307</v>
@@ -10187,7 +10191,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>93</v>
@@ -10205,7 +10209,7 @@
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>312</v>
@@ -10222,10 +10226,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10251,13 +10255,13 @@
         <v>389</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M68" t="s" s="2">
         <v>391</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>393</v>
@@ -10309,7 +10313,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10327,7 +10331,7 @@
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>396</v>
@@ -10344,10 +10348,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10373,13 +10377,13 @@
         <v>223</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O69" t="s" s="2">
         <v>403</v>
@@ -10431,7 +10435,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10466,10 +10470,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10553,7 +10557,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10588,10 +10592,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10617,10 +10621,10 @@
         <v>83</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>469</v>
@@ -10675,7 +10679,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
